--- a/Documents/Requirements and Specifications/Requirements_and_specifications.xlsx
+++ b/Documents/Requirements and Specifications/Requirements_and_specifications.xlsx
@@ -5,13 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Definitions" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Contents" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Requirements" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Specifications" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="RQ-SCON" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="SP-SCON" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Specifications" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="RQ-Power ON OFF" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="SP-Power ON OFF" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="102">
   <si>
     <t xml:space="preserve">Persons</t>
   </si>
@@ -61,6 +65,12 @@
     <t xml:space="preserve">The person that knows the needs of user and configures device to personalize the Oradio</t>
   </si>
   <si>
+    <t xml:space="preserve">All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All persons</t>
+  </si>
+  <si>
     <t xml:space="preserve">Requirements </t>
   </si>
   <si>
@@ -142,15 +152,135 @@
     <t xml:space="preserve">SP-USB-001</t>
   </si>
   <si>
+    <t xml:space="preserve">RQ-SCON-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to connect to a listed Oradio device to play my playlist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-SCON-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-SCON-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When Oradio is in OFF state, I want the playlist to start playing when I touch the ON button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Spotify playlist should be kept alive when I switch OFF the Oradio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So I can listen to my Spotify playlist when switching ON the oradio again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When I switch ON the oradio and an Spotify playlist was alive, I want to listen to this playlist again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So I can listen to my Spotify playlist where I left it at switch OFF time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When I switch ON the oradio and a spotify playlist was alive, the playlist should continue at the last position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So I can listen to my spotify playlist again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When I close my Spotify App or Spotify Web my playlist on the Oradio should continue to play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So I can keep listening to the Spotify playlist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When a Preset button is pressed, the Oradio should play the associated music, but should also keep the Spotify playlist alive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So I can keep return to my Spotify playlist if I want to.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When Oradio is playing a Spotify playlist and Spotify App or Spotify Web is opened again, the green status bar at the bottom should indicate that it is playing on the Oradio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So I am informed that the connection is re-established</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-SCON-010</t>
+  </si>
+  <si>
     <t xml:space="preserve">SPEC-ID</t>
   </si>
   <si>
     <t xml:space="preserve">REQ-ID</t>
   </si>
   <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
     <t xml:space="preserve">Description</t>
   </si>
   <si>
+    <t xml:space="preserve">Test Specification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Oradio should allow the requested connection from the Spotify Connect application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The connection should be established in all possible Oradio states.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Oradio should use the Audio/Video Receiver type for the device list in spotify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select the type &lt;avr&gt; in the librespot.service configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-SCON-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Oradio sould be uniquely listed in the spotify device list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In case multiple Oradio’s are on same network, a mDNS naming resolution protocol shall be used, to uniquely identify an Oradio. Naming convention is:Oradio, Oradio-1,etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Oradio shall define the device-type AVR in the librespot configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-SCON-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-SCON-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If Oradio has a device name configured via the web-interface, this name should be used as device name for spotify. E.g. device-name=Oradio-Jan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the web-interface there shall be field to enter the device-name of the Oradio. This device-name shall be used in librespot as new name. </t>
+  </si>
+  <si>
     <t xml:space="preserve">SP-SPOT-001</t>
   </si>
   <si>
@@ -166,30 +296,15 @@
     <t xml:space="preserve">REQ-SPOT-002</t>
   </si>
   <si>
-    <t xml:space="preserve">The Oradio should use the Audio/Video Receiver type for the device list in spotify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Oradio shall define the device-type AVR in the librespot configuration</t>
-  </si>
-  <si>
     <t xml:space="preserve">REQ-SPOT-003</t>
   </si>
   <si>
-    <t xml:space="preserve">The Oradio sould be uniquely listed in the spotify device list</t>
-  </si>
-  <si>
     <t xml:space="preserve">In case multiple Oradio’s are on same network, a mDNS naming resolution protocol shall be used, to uniquely identify an Oradio. Naming convention is:oradio, oradio-1,etc.</t>
   </si>
   <si>
     <t xml:space="preserve">REQ-SPOT-004</t>
   </si>
   <si>
-    <t xml:space="preserve">If Oradio has a device name configured via the web-interface, this name should be used as device name for spotify. E.g. device-name=Oradio-Jan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On the web-interface there shall be field to enter the device-name of the Oradio. This device-name shall be used in librespot as new name. </t>
-  </si>
-  <si>
     <t xml:space="preserve">SP-SPOT-003</t>
   </si>
   <si>
@@ -200,6 +315,24 @@
   </si>
   <si>
     <t xml:space="preserve">Following formats should be supported: MP3, WAV and WMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mains power Requirements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-MPOW-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-MPOW-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RQ-MPOW-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mains power Specifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-MPOW-001</t>
   </si>
 </sst>
 </file>
@@ -214,7 +347,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -236,14 +368,12 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -313,64 +443,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -383,6 +521,31 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDEE6EF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFDBB6"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -557,59 +720,67 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:B7"/>
+  <dimension ref="A2:B8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="77.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.31"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -637,34 +808,34 @@
   <dimension ref="C2:D4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="2.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.66"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
+      <c r="C2" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -692,240 +863,244 @@
   <dimension ref="A2:F21"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="27.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.37"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="D5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="E13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="34.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="34.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="C14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="5"/>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A11:E11"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B6:B8 B14:B16" type="list">
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B6" type="list">
+      <formula1>Definitions!$A$3:$A$8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B7:B8 B14:B16" type="list">
       <formula1>Definitions!$A$3:$A$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -949,162 +1124,639 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A2:F16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="27.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.37"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="22.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="38.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="38.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B6:B7 B9:B15" type="list">
+      <formula1>Definitions!$A$3:$A$8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B8" type="list">
+      <formula1>Definitions!$A$3:$A$7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E6" location="SP-SCON!A5" display="SP-SCON-001"/>
+    <hyperlink ref="E7" location="SP-SCON!A6" display="SP-SCON-002"/>
+    <hyperlink ref="E8" location="SP-SCON!A7" display="SP-SCON-002"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:G15"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="37.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.37"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="11" t="str">
+        <f aca="false">HYPERLINK("file:../Test Specifications/VS Functional Tests Oradio3.xlsx#Spotify Connect.A1","SCON-01")</f>
+        <v>SCON-01</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="34.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="57" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="38.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="57" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A3:D17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50.97"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="31.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="34.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="45.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>58</v>
+      <c r="B16" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1120,4 +1772,402 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A4:F25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.32"/>
+  </cols>
+  <sheetData>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="34.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A18:D18"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B7:B9" type="list">
+      <formula1>Definitions!$A$3:$A$8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E9" location="Specifications!A7" display="SP-SPOT-002"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A4:F25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.32"/>
+  </cols>
+  <sheetData>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="34.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A18:D18"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B7:B9" type="list">
+      <formula1>Definitions!$A$3:$A$8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E9" location="Specifications!A7" display="SP-SPOT-002"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>